--- a/merged_b1_full_cypress_coverage.xlsx
+++ b/merged_b1_full_cypress_coverage.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
